--- a/附表1和2_计算结果.xlsx
+++ b/附表1和2_计算结果.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,6 +46,11 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -61,7 +66,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -75,11 +80,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -90,11 +123,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -460,31 +496,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:W17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="9.1" customWidth="1" min="4" max="4"/>
-    <col width="15.6" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="15.6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="5.2" customWidth="1" min="3" max="3"/>
+    <col width="5.2" customWidth="1" min="4" max="4"/>
+    <col width="7.800000000000001" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
     <col width="11.7" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="10.4" customWidth="1" min="15" max="15"/>
-    <col width="11.7" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="10.4" customWidth="1" min="16" max="16"/>
+    <col width="5.2" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="18" max="18"/>
+    <col width="5.2" customWidth="1" min="19" max="19"/>
+    <col width="5" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>附表1  A-B 区段区间通过能力计算表</t>
+          <t>A-B 区段区间通过能力计算表         附表 1</t>
         </is>
       </c>
     </row>
@@ -506,13 +549,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>距离
-(km)</t>
+          <t>区间距离</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>区间运行时间 (min)</t>
+          <t>区间运行时间</t>
         </is>
       </c>
       <c r="F2" s="2" t="n"/>
@@ -520,7 +562,8 @@
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>车站间隔时间 (min)</t>
+          <t>车站间隔时间
+（分）</t>
         </is>
       </c>
       <c r="J2" s="2" t="n"/>
@@ -528,8 +571,8 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>t技停
-(min)</t>
+          <t>技术作业
+停站时间</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -539,14 +582,40 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>T周
-(min)</t>
+          <t>T周</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>N平行
-(对/天)</t>
+          <t>平行图
+最大能力</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>旅客列车</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>摘挂列车</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>n非货</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>n非</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>附记</t>
         </is>
       </c>
     </row>
@@ -557,12 +626,12 @@
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>上行</t>
+          <t>上</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>下行</t>
+          <t>下</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -587,85 +656,95 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>τ空1</t>
+          <t> </t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>τ空2</t>
+          <t> </t>
         </is>
       </c>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>ε客</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>n客</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>ε摘</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>n摘</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n"/>
+      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>A-a</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>单线</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>半自动</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="E4" s="3" t="n">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>站内会车</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>27.1</v>
-      </c>
+      <c r="R4" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="U4" s="2" t="n"/>
+      <c r="V4" s="2" t="n"/>
+      <c r="W4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>a-b</t>
+          <t>A-a</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -679,13 +758,13 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>2</v>
@@ -699,35 +778,42 @@
       <c r="J5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>站内会车</t>
+          <t>(a)两端不停车通过</t>
         </is>
       </c>
       <c r="O5" s="3" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>30</v>
-      </c>
+        <v>27.1</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>b-c</t>
+          <t>a-b</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -741,13 +827,13 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>2</v>
@@ -761,35 +847,42 @@
       <c r="J6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>站内会车</t>
+          <t>(c)下行不停车通过</t>
         </is>
       </c>
       <c r="O6" s="3" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>34.5</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" s="3" t="inlineStr"/>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>c-d</t>
+          <t>b-c</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -803,13 +896,13 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="E7" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="F7" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>2</v>
@@ -823,35 +916,42 @@
       <c r="J7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>站内会车</t>
+          <t>(d)上行不停车通过</t>
         </is>
       </c>
       <c r="O7" s="3" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>28.2</v>
-      </c>
+        <v>34.5</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" s="3" t="inlineStr"/>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>d-e</t>
+          <t>c-d</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -865,13 +965,13 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E8" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="E8" s="3" t="n">
-        <v>23</v>
-      </c>
       <c r="F8" s="3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>2</v>
@@ -885,35 +985,42 @@
       <c r="J8" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>站内会车</t>
+          <t>(a)两端不停车通过</t>
         </is>
       </c>
       <c r="O8" s="3" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>23</v>
-      </c>
+        <v>28.2</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" s="3" t="inlineStr"/>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>e-B</t>
+          <t>d-e</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -927,13 +1034,13 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>2</v>
@@ -947,94 +1054,196 @@
       <c r="J9" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>站内会车</t>
+          <t>(c)下行不停车通过</t>
         </is>
       </c>
       <c r="O9" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" s="3" t="inlineStr"/>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>e-B</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>单线</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>半自动</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>(d)上行不停车通过</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="P9" s="3" t="n">
+      <c r="P10" s="3" t="n">
         <v>38.3</v>
       </c>
-    </row>
-    <row r="10"/>
+      <c r="Q10" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" s="3" t="inlineStr"/>
+      <c r="V10" s="3" t="inlineStr"/>
+      <c r="W10" s="3" t="inlineStr"/>
+    </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>限制区间: d-e (T周=60 min)  |  可用时间: 1440-60=1380 min  |  N平行 = 1380/60 = 23 对/天</t>
-        </is>
-      </c>
+          <t>限制区间: d-e  T周=60 min  可用时间=1440-60=1380 min  N平行=1380/60=23 对/天</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
+      <c r="Q11" s="5" t="n"/>
+      <c r="R11" s="5" t="n"/>
+      <c r="S11" s="5" t="n"/>
+      <c r="T11" s="5" t="n"/>
+      <c r="U11" s="5" t="n"/>
+      <c r="V11" s="5" t="n"/>
+      <c r="W11" s="6" t="n"/>
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>非平行运行图通过能力计算:</t>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>非平行运行图通过能力计算</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>旅客列车扣除: ε客×n客 = 1.3×2 = 2.6</t>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>ε客=1.3  n客=2  扣除: 1.3×2=2.6</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>摘挂列车追加扣除: (ε摘挂-1)×n摘挂 = 0.5×3 = 1.5</t>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>ε摘=1.5  n摘=3  追加扣除: (1.5-1)×3=1.5</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>快货列车追加扣除: (ε快货-1)×n快货 = 0.6×6 = 3.6</t>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>ε快货=1.6  n快货=6  追加扣除: (1.6-1)×6=3.6</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>总扣除: 7.7 对  |  N非平行 = 23 - 7.7 = 15.3 → 取整 15 对/天</t>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>总扣除=7.7 对   N非平行=23-7.7=15.3  取整=15 对/天</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A11:P11"/>
-    <mergeCell ref="A15:P15"/>
-    <mergeCell ref="A13:P13"/>
-    <mergeCell ref="A14:P14"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="A17:P17"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A2:A3"/>
+  <mergeCells count="22">
+    <mergeCell ref="A13:W13"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="W2:W4"/>
+    <mergeCell ref="A15:W15"/>
+    <mergeCell ref="O2:O4"/>
+    <mergeCell ref="A11:W11"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="V2:V4"/>
+    <mergeCell ref="A16:W16"/>
     <mergeCell ref="I2:L2"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A16:P16"/>
-    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="U2:U4"/>
+    <mergeCell ref="M2:M4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="P2:P4"/>
+    <mergeCell ref="A14:W14"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="A17:W17"/>
+    <mergeCell ref="N2:N4"/>
     <mergeCell ref="E2:H2"/>
-    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1046,40 +1255,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R32"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="10.4" customWidth="1" min="4" max="4"/>
-    <col width="10.4" customWidth="1" min="5" max="5"/>
-    <col width="10.4" customWidth="1" min="6" max="6"/>
-    <col width="10.4" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="10.4" customWidth="1" min="11" max="11"/>
-    <col width="10.4" customWidth="1" min="12" max="12"/>
-    <col width="10.4" customWidth="1" min="13" max="13"/>
-    <col width="10.4" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="7.800000000000001" customWidth="1" min="2" max="2"/>
+    <col width="6.5" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="9.1" customWidth="1" min="8" max="8"/>
+    <col width="7.800000000000001" customWidth="1" min="9" max="9"/>
+    <col width="6.5" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="10.4" customWidth="1" min="15" max="15"/>
+    <col width="10.4" customWidth="1" min="16" max="16"/>
+    <col width="10.4" customWidth="1" min="17" max="17"/>
+    <col width="10.4" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>附表2  A-B 区段运行图质量指标计算表</t>
+          <t>A-B 区段运行图质量指标计算表         附表 2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>下行方向</t>
+          <t>下 行 方 向</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1090,7 +1299,7 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>上行方向</t>
+          <t>上 行 方 向</t>
         </is>
       </c>
       <c r="I2" s="2" t="n"/>
@@ -1101,7 +1310,7 @@
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>机车</t>
+          <t>机  车</t>
         </is>
       </c>
       <c r="P2" s="2" t="n"/>
@@ -1116,357 +1325,271 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>时    间</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>列车公里</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>车次</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>时    间</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>列车公里</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>在B站
+停留时间</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>从A站
+牵引车次</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>从A站
+出发时间</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>在A站
+停留时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>由A发</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>到B</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>在途
-(min)</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>运行
-(min)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>停站
-(min)</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>列公里
-(km)</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>车次</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>到n</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>在途</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>其  中</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>由B发</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>到A</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>在途
-(min)</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>运行
-(min)</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>停站
-(min)</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>列公里
-(km)</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>B站停留
-(min)</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>牵引车次</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>A站出发</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>A站停留
-(min)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>30001</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>01:10</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>03:18</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="F4" s="3" t="n">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>在途</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>其  中</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>运行</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>停站</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>运行</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>停站</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
+      <c r="P5" s="2" t="n"/>
+      <c r="Q5" s="2" t="n"/>
+      <c r="R5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="G4" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>10004</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>06:35</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>08:25</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>10004</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>30002</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>03:20</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>05:28</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>10005</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>10005</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>30003</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>07:38</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>40045</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>185</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>172</v>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t>40045</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t>17:25</t>
-        </is>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>230</v>
+      <c r="R6" s="2" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>40035</t>
+          <t>30001</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>01:10</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>03:18</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>203</v>
+        <v>128</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>111</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>76</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>100012</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>06:35</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="K7" s="3" t="n">
@@ -1482,36 +1605,36 @@
         <v>76</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>127</v>
+        <v>197</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>100012</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="R7" s="3" t="n">
-        <v>215</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>30004</t>
+          <t>30002</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>03:20</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>05:28</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1528,17 +1651,17 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>100013</t>
+          <t>10005</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="K8" s="3" t="n">
@@ -1554,38 +1677,36 @@
         <v>76</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>262</v>
+        <v>197</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>100013</t>
+          <t>10005</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>30005</t>
+          <t>30003</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1602,205 +1723,181 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>100014</t>
+          <t>40045</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>110</v>
+        <v>185</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>93</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>76</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>262</v>
+        <v>172</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>100014</t>
+          <t>40045</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>230</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>86001</t>
+          <t>40035</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>128</v>
+        <v>203</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>111</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>76</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100012</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>127</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100012</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>215</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>40036</t>
+          <t>30004</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>203</v>
+        <v>128</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>111</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>76</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100013</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>262</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100013</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -1817,17 +1914,17 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>86002</t>
+          <t>30005</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1844,47 +1941,37 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100014</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>262</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100014</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -1901,17 +1988,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>86003</t>
+          <t>86001</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1985,65 +2072,65 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>40036</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>76</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>02:15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>04:05</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>76</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
@@ -2052,7 +2139,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -2069,65 +2156,65 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>86002</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>76</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>04:25</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>06:15</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>76</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
@@ -2136,7 +2223,7 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -2153,330 +2240,441 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>86003</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>76</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>10002</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>04:05</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>10002</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>10003</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>04:25</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>10003</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
           <t>10006</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>10:55</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>12:45</t>
         </is>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K19" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L19" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M19" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="N16" s="3" t="n">
+      <c r="N19" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr">
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
         <is>
           <t>10006</t>
         </is>
       </c>
-      <c r="Q16" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R16" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
         <v>1430</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E20" s="4" t="n">
         <v>1110</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F20" s="4" t="n">
         <v>320</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="G20" s="4" t="n">
         <v>760</v>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K17" s="6" t="n">
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="n">
         <v>1065</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="L20" s="4" t="n">
         <v>837</v>
       </c>
-      <c r="M17" s="6" t="n">
+      <c r="M20" s="4" t="n">
         <v>228</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="N20" s="4" t="n">
         <v>684</v>
       </c>
-      <c r="O17" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>指标</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>下行</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>上行</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>合计</t>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>统计列车数</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>技术速度 (km/h)</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>44.5</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>旅行速度 (km/h)</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>34.7</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>速度系数</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>0.7762</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>0.7859</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>0.7804</v>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>机车指标</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>机车交路数</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>平均B站停留 (min)</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>平均A站停留 (min)</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>平均周转时间 (min)</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>机车日车公里-单台 (km)</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>机车日车公里-总 (km)</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>1432</v>
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>注：每一行上行方向车次按机车折返交路的顺序填写</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="17">
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="H3:H5"/>
+    <mergeCell ref="A21:R21"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="O3:O5"/>
+    <mergeCell ref="Q3:Q5"/>
+    <mergeCell ref="H2:N2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="P3:P5"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="O2:R2"/>
     <mergeCell ref="A1:R1"/>
-    <mergeCell ref="H2:N2"/>
+    <mergeCell ref="R3:R5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/附表1和2_计算结果.xlsx
+++ b/附表1和2_计算结果.xlsx
@@ -1278,14 +1278,14 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>ε快货=1.6  n快货=6  追加扣除: (1.6-1)×6=3.6</t>
+          <t>ε快货=1.6  n快货=3  追加扣除: (1.6-1)×3=1.8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>总扣除=6.7 对   N非平行=22-6.7=15.3  取整=15 对/天</t>
+          <t>总扣除=4.9 对   N非平行=22-4.9=17.1  取整=17 对/天</t>
         </is>
       </c>
     </row>
